--- a/Result/profitability/6148.xlsx
+++ b/Result/profitability/6148.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3025</v>
+        <v>0.2375</v>
       </c>
       <c r="N2" t="n">
-        <v>21.645</v>
+        <v>22.3025</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2325</v>
+        <v>0.2025</v>
       </c>
       <c r="N3" t="n">
-        <v>20.20125</v>
+        <v>20.475</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.18125</v>
+        <v>0.1725</v>
       </c>
       <c r="N4" t="n">
-        <v>18.65875</v>
+        <v>19.19875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.36</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01000000000000004</v>
+        <v>-0.03250000000000003</v>
       </c>
       <c r="N5" t="n">
-        <v>15.71625</v>
+        <v>15.49875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03250000000000004</v>
+        <v>-0.05250000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>13.5375</v>
+        <v>14.245</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08250000000000005</v>
+        <v>-0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>12.05375</v>
+        <v>12.58875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.01</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.16125</v>
+        <v>-0.1575</v>
       </c>
       <c r="N8" t="n">
-        <v>10.73</v>
+        <v>10.76</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>-0.05750000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>8.244999999999999</v>
+        <v>8.245000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9800,6 +9800,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6148</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>123</v>
+      </c>
+      <c r="D75" t="n">
+        <v>91</v>
+      </c>
+      <c r="E75" t="n">
+        <v>32</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.31375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.2399999999999984</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.009374999999999911</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.739999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.06308919506889044</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
